--- a/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-find-lists-response.xlsx
+++ b/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-find-lists-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:19:16+00:00</t>
+    <t>2026-08-06T13:23:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-find-lists-response.xlsx
+++ b/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-find-lists-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:23:45+00:00</t>
+    <t>2026-08-06T13:28:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-find-lists-response.xlsx
+++ b/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-find-lists-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:28:00+00:00</t>
+    <t>2026-08-06T13:33:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-find-lists-response.xlsx
+++ b/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-find-lists-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:33:58+00:00</t>
+    <t>2026-08-06T13:37:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-find-lists-response.xlsx
+++ b/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-find-lists-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:37:30+00:00</t>
+    <t>2026-08-06T13:40:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-find-lists-response.xlsx
+++ b/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-find-lists-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:40:23+00:00</t>
+    <t>2026-08-06T13:54:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-find-lists-response.xlsx
+++ b/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-find-lists-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:54:33+00:00</t>
+    <t>2026-08-06T13:55:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-find-lists-response.xlsx
+++ b/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-find-lists-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:55:54+00:00</t>
+    <t>2026-08-06T14:05:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-find-lists-response.xlsx
+++ b/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-find-lists-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T14:05:46+00:00</t>
+    <t>2026-08-06T14:06:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-find-lists-response.xlsx
+++ b/nr-securitylabel-slicing-123/ig/StructureDefinition-pdsm-find-lists-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T14:06:47+00:00</t>
+    <t>2026-08-06T14:07:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
